--- a/psychopy_exp_files/sequences/retrieval_block3_fixed-middle-10_56.xlsx
+++ b/psychopy_exp_files/sequences/retrieval_block3_fixed-middle-10_56.xlsx
@@ -552,12 +552,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -585,7 +585,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
@@ -630,12 +630,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>2</v>
@@ -690,12 +690,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
@@ -768,12 +768,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
@@ -828,12 +828,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>
@@ -906,12 +906,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -925,7 +925,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>2</v>
@@ -966,12 +966,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -999,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>1.2</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1413,7 +1413,7 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
         <v>1.2</v>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>1.2</v>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>2</v>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
         <v>1.2</v>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
         <v>2</v>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1827,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>1.2</v>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
         <v>1.2</v>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
         <v>2</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -2103,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
         <v>1.2</v>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>2</v>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2241,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>1.2</v>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>2</v>
@@ -2346,12 +2346,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
         <v>1.2</v>
@@ -2424,12 +2424,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
         <v>2</v>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -2517,7 +2517,7 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
         <v>1.2</v>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
         <v>2</v>
@@ -2622,12 +2622,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>1.2</v>
@@ -2700,12 +2700,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
         <v>2</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2793,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
         <v>1.2</v>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
         <v>2</v>
@@ -2898,12 +2898,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2931,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
         <v>1.2</v>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O37" t="n">
         <v>2</v>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
         <v>1.2</v>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
         <v>2</v>
@@ -3174,12 +3174,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -3207,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>1.2</v>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O41" t="n">
         <v>2</v>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
         <v>1.2</v>
@@ -3390,12 +3390,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43" t="n">
         <v>2</v>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -3483,7 +3483,7 @@
         <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O44" t="n">
         <v>1.2</v>
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O45" t="n">
         <v>2</v>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
         <v>1.2</v>
@@ -3666,12 +3666,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
         <v>2</v>
@@ -3726,12 +3726,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -3759,7 +3759,7 @@
         <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
         <v>1.2</v>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O49" t="n">
         <v>2</v>
@@ -3864,12 +3864,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -3897,7 +3897,7 @@
         <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" t="n">
         <v>1.2</v>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
         <v>2</v>
@@ -4002,12 +4002,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -4035,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>1.2</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
@@ -4218,12 +4218,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O55" t="n">
         <v>2</v>
@@ -4278,12 +4278,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -4311,7 +4311,7 @@
         <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O56" t="n">
         <v>1.2</v>
@@ -4356,12 +4356,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O57" t="n">
         <v>2</v>
@@ -4416,12 +4416,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -4449,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O58" t="n">
         <v>1.2</v>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O59" t="n">
         <v>2</v>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O60" t="n">
         <v>1.2</v>
@@ -4632,12 +4632,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O61" t="n">
         <v>2</v>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -4725,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O62" t="n">
         <v>1.2</v>
@@ -4770,12 +4770,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
         <v>2</v>
@@ -4830,12 +4830,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -4863,7 +4863,7 @@
         <v>1</v>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O64" t="n">
         <v>1.2</v>
@@ -4908,12 +4908,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O65" t="n">
         <v>2</v>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O66" t="n">
         <v>1.2</v>
@@ -5046,12 +5046,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O67" t="n">
         <v>2</v>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -5139,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O68" t="n">
         <v>1.2</v>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O69" t="n">
         <v>2</v>
@@ -5244,12 +5244,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -5277,7 +5277,7 @@
         <v>1</v>
       </c>
       <c r="N70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O70" t="n">
         <v>1.2</v>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -5382,12 +5382,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -5415,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
         <v>1.2</v>
@@ -5460,12 +5460,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
         <v>2</v>
@@ -5520,12 +5520,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -5553,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O74" t="n">
         <v>1.2</v>
@@ -5598,12 +5598,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O75" t="n">
         <v>2</v>
@@ -5658,12 +5658,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O76" t="n">
         <v>1.2</v>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O77" t="n">
         <v>2</v>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -5829,7 +5829,7 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O78" t="n">
         <v>1.2</v>
@@ -5874,12 +5874,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O79" t="n">
         <v>2</v>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -5967,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O80" t="n">
         <v>1.2</v>
@@ -6012,12 +6012,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O81" t="n">
         <v>2</v>
@@ -6072,12 +6072,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -6105,7 +6105,7 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
         <v>1.2</v>
@@ -6150,12 +6150,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O83" t="n">
         <v>2</v>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -6243,7 +6243,7 @@
         <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O84" t="n">
         <v>1.2</v>
@@ -6288,12 +6288,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O85" t="n">
         <v>2</v>
@@ -6348,12 +6348,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -6381,7 +6381,7 @@
         <v>1</v>
       </c>
       <c r="N86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O86" t="n">
         <v>1.2</v>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O87" t="n">
         <v>2</v>
@@ -6486,12 +6486,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -6519,7 +6519,7 @@
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O88" t="n">
         <v>1.2</v>
@@ -6564,12 +6564,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O89" t="n">
         <v>2</v>
@@ -6624,12 +6624,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -6657,7 +6657,7 @@
         <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O90" t="n">
         <v>1.2</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O91" t="n">
         <v>2</v>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O92" t="n">
         <v>1.2</v>
@@ -6840,12 +6840,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O93" t="n">
         <v>2</v>
@@ -6900,12 +6900,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -6933,7 +6933,7 @@
         <v>1</v>
       </c>
       <c r="N94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O94" t="n">
         <v>1.2</v>
@@ -6978,12 +6978,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O95" t="n">
         <v>2</v>
@@ -7038,12 +7038,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -7071,7 +7071,7 @@
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O96" t="n">
         <v>1.2</v>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O97" t="n">
         <v>2</v>
@@ -7176,12 +7176,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -7209,7 +7209,7 @@
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O98" t="n">
         <v>1.2</v>
@@ -7254,12 +7254,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O99" t="n">
         <v>2</v>
@@ -7314,12 +7314,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -7347,7 +7347,7 @@
         <v>1</v>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O100" t="n">
         <v>1.2</v>
@@ -7392,12 +7392,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -7485,7 +7485,7 @@
         <v>1</v>
       </c>
       <c r="N102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O102" t="n">
         <v>1.2</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O103" t="n">
         <v>2</v>
@@ -7590,12 +7590,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O104" t="n">
         <v>1.2</v>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O105" t="n">
         <v>2</v>
@@ -7728,12 +7728,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -7761,7 +7761,7 @@
         <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O106" t="n">
         <v>1.2</v>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O107" t="n">
         <v>2</v>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -7899,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="N108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O108" t="n">
         <v>1.2</v>
@@ -7944,12 +7944,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O109" t="n">
         <v>2</v>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -8037,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O110" t="n">
         <v>1.2</v>
@@ -8082,12 +8082,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O111" t="n">
         <v>2</v>
@@ -8142,12 +8142,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -8175,7 +8175,7 @@
         <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O112" t="n">
         <v>1.2</v>
@@ -8220,12 +8220,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O113" t="n">
         <v>2</v>
@@ -8280,12 +8280,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -8313,7 +8313,7 @@
         <v>1</v>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O114" t="n">
         <v>1.2</v>
@@ -8358,12 +8358,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
@@ -8377,7 +8377,7 @@
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O115" t="n">
         <v>2</v>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -8451,7 +8451,7 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O116" t="n">
         <v>1.2</v>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O117" t="n">
         <v>2</v>
@@ -8556,12 +8556,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O118" t="n">
         <v>1.2</v>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O119" t="n">
         <v>2</v>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -8727,7 +8727,7 @@
         <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O120" t="n">
         <v>1.2</v>
@@ -8772,12 +8772,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O121" t="n">
         <v>2</v>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
@@ -8865,7 +8865,7 @@
         <v>1</v>
       </c>
       <c r="N122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O122" t="n">
         <v>1.2</v>
@@ -8910,12 +8910,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O123" t="n">
         <v>2</v>
@@ -8970,12 +8970,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
@@ -9003,7 +9003,7 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O124" t="n">
         <v>1.2</v>
@@ -9048,12 +9048,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O125" t="n">
         <v>2</v>
@@ -9108,12 +9108,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -9141,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O126" t="n">
         <v>1.2</v>
@@ -9186,12 +9186,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O127" t="n">
         <v>2</v>
@@ -9246,12 +9246,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -9279,7 +9279,7 @@
         <v>1</v>
       </c>
       <c r="N128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O128" t="n">
         <v>1.2</v>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O129" t="n">
         <v>2</v>
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -9417,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O130" t="n">
         <v>1.2</v>
@@ -9462,12 +9462,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O131" t="n">
         <v>2</v>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -9555,7 +9555,7 @@
         <v>1</v>
       </c>
       <c r="N132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O132" t="n">
         <v>1.2</v>
@@ -9600,12 +9600,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O133" t="n">
         <v>2</v>
@@ -9660,12 +9660,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -9693,7 +9693,7 @@
         <v>1</v>
       </c>
       <c r="N134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O134" t="n">
         <v>1.2</v>
@@ -9738,12 +9738,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O135" t="n">
         <v>2</v>
@@ -9798,12 +9798,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -9831,7 +9831,7 @@
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O136" t="n">
         <v>1.2</v>
@@ -9876,12 +9876,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O137" t="n">
         <v>2</v>
@@ -9936,12 +9936,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -9969,7 +9969,7 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O138" t="n">
         <v>1.2</v>
@@ -10014,12 +10014,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O139" t="n">
         <v>2</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -10107,7 +10107,7 @@
         <v>1</v>
       </c>
       <c r="N140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O140" t="n">
         <v>1.2</v>
@@ -10152,12 +10152,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O141" t="n">
         <v>2</v>
@@ -10212,12 +10212,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -10245,7 +10245,7 @@
         <v>1</v>
       </c>
       <c r="N142" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O142" t="n">
         <v>1.2</v>
@@ -10290,12 +10290,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O143" t="n">
         <v>2</v>
@@ -10350,12 +10350,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -10383,7 +10383,7 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O144" t="n">
         <v>1.2</v>
@@ -10428,12 +10428,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O145" t="n">
         <v>2</v>
@@ -10488,12 +10488,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -10521,7 +10521,7 @@
         <v>1</v>
       </c>
       <c r="N146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O146" t="n">
         <v>1.2</v>
@@ -10566,12 +10566,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -10585,7 +10585,7 @@
       </c>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O147" t="n">
         <v>2</v>
@@ -10626,12 +10626,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
@@ -10659,7 +10659,7 @@
         <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O148" t="n">
         <v>1.2</v>
@@ -10704,12 +10704,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O149" t="n">
         <v>2</v>
@@ -10764,12 +10764,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -10797,7 +10797,7 @@
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O150" t="n">
         <v>1.2</v>
@@ -10842,12 +10842,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -10861,7 +10861,7 @@
       </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O151" t="n">
         <v>2</v>
@@ -10902,12 +10902,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -10935,7 +10935,7 @@
         <v>1</v>
       </c>
       <c r="N152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O152" t="n">
         <v>1.2</v>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O153" t="n">
         <v>2</v>
@@ -11040,12 +11040,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
@@ -11073,7 +11073,7 @@
         <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O154" t="n">
         <v>1.2</v>
@@ -11118,12 +11118,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -11137,7 +11137,7 @@
       </c>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O155" t="n">
         <v>2</v>
@@ -11178,12 +11178,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
@@ -11211,7 +11211,7 @@
         <v>1</v>
       </c>
       <c r="N156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O156" t="n">
         <v>1.2</v>
@@ -11256,12 +11256,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O157" t="n">
         <v>2</v>
@@ -11316,12 +11316,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
@@ -11349,7 +11349,7 @@
         <v>1</v>
       </c>
       <c r="N158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O158" t="n">
         <v>1.2</v>
@@ -11394,12 +11394,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O159" t="n">
         <v>2</v>
@@ -11454,12 +11454,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
@@ -11487,7 +11487,7 @@
         <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O160" t="n">
         <v>1.2</v>
@@ -11532,12 +11532,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O161" t="n">
         <v>2</v>
@@ -11592,12 +11592,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
@@ -11625,7 +11625,7 @@
         <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O162" t="n">
         <v>1.2</v>
@@ -11670,12 +11670,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O163" t="n">
         <v>2</v>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -11763,7 +11763,7 @@
         <v>1</v>
       </c>
       <c r="N164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O164" t="n">
         <v>1.2</v>
@@ -11808,12 +11808,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O165" t="n">
         <v>2</v>
@@ -11868,12 +11868,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
@@ -11901,7 +11901,7 @@
         <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O166" t="n">
         <v>1.2</v>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O167" t="n">
         <v>2</v>
@@ -12006,12 +12006,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
@@ -12039,7 +12039,7 @@
         <v>1</v>
       </c>
       <c r="N168" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O168" t="n">
         <v>1.2</v>
@@ -12084,12 +12084,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O169" t="n">
         <v>2</v>
@@ -12144,12 +12144,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
@@ -12177,7 +12177,7 @@
         <v>1</v>
       </c>
       <c r="N170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O170" t="n">
         <v>1.2</v>
@@ -12222,12 +12222,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O171" t="n">
         <v>2</v>
@@ -12282,12 +12282,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -12315,7 +12315,7 @@
         <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O172" t="n">
         <v>1.2</v>
@@ -12360,12 +12360,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O173" t="n">
         <v>2</v>
@@ -12420,12 +12420,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
@@ -12453,7 +12453,7 @@
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O174" t="n">
         <v>1.2</v>
@@ -12498,12 +12498,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
@@ -12517,7 +12517,7 @@
       </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O175" t="n">
         <v>2</v>
@@ -12558,12 +12558,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -12591,7 +12591,7 @@
         <v>1</v>
       </c>
       <c r="N176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O176" t="n">
         <v>1.2</v>
@@ -12636,12 +12636,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O177" t="n">
         <v>2</v>
@@ -12696,12 +12696,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O178" t="n">
         <v>1.2</v>
@@ -12774,12 +12774,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O179" t="n">
         <v>2</v>
@@ -12834,12 +12834,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
@@ -12867,7 +12867,7 @@
         <v>1</v>
       </c>
       <c r="N180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O180" t="n">
         <v>1.2</v>
@@ -12912,12 +12912,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
@@ -12931,7 +12931,7 @@
       </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O181" t="n">
         <v>2</v>
@@ -12972,12 +12972,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
@@ -13005,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O182" t="n">
         <v>1.2</v>
@@ -13050,12 +13050,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
@@ -13069,7 +13069,7 @@
       </c>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O183" t="n">
         <v>2</v>
@@ -13110,12 +13110,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
@@ -13143,7 +13143,7 @@
         <v>1</v>
       </c>
       <c r="N184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O184" t="n">
         <v>1.2</v>
@@ -13188,12 +13188,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
@@ -13207,7 +13207,7 @@
       </c>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O185" t="n">
         <v>2</v>
@@ -13248,12 +13248,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
@@ -13281,7 +13281,7 @@
         <v>1</v>
       </c>
       <c r="N186" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O186" t="n">
         <v>1.2</v>
@@ -13326,12 +13326,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
@@ -13345,7 +13345,7 @@
       </c>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O187" t="n">
         <v>2</v>
@@ -13386,12 +13386,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
@@ -13419,7 +13419,7 @@
         <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O188" t="n">
         <v>1.2</v>
@@ -13464,12 +13464,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O189" t="n">
         <v>2</v>
@@ -13524,12 +13524,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
@@ -13557,7 +13557,7 @@
         <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O190" t="n">
         <v>1.2</v>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O191" t="n">
         <v>2</v>
@@ -13662,12 +13662,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
@@ -13695,7 +13695,7 @@
         <v>1</v>
       </c>
       <c r="N192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O192" t="n">
         <v>1.2</v>
@@ -13740,12 +13740,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O193" t="n">
         <v>2</v>
@@ -13800,12 +13800,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
@@ -13833,7 +13833,7 @@
         <v>1</v>
       </c>
       <c r="N194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O194" t="n">
         <v>1.2</v>
@@ -13878,12 +13878,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O195" t="n">
         <v>2</v>
@@ -13938,12 +13938,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
@@ -13971,7 +13971,7 @@
         <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O196" t="n">
         <v>1.2</v>
@@ -14016,12 +14016,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
@@ -14035,7 +14035,7 @@
       </c>
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O197" t="n">
         <v>2</v>
@@ -14076,12 +14076,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
@@ -14109,7 +14109,7 @@
         <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O198" t="n">
         <v>1.2</v>
@@ -14154,12 +14154,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O199" t="n">
         <v>2</v>
@@ -14214,12 +14214,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
@@ -14247,7 +14247,7 @@
         <v>1</v>
       </c>
       <c r="N200" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O200" t="n">
         <v>1.2</v>
@@ -14292,12 +14292,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O201" t="n">
         <v>2</v>
@@ -14352,12 +14352,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
@@ -14385,7 +14385,7 @@
         <v>1</v>
       </c>
       <c r="N202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O202" t="n">
         <v>1.2</v>
@@ -14430,12 +14430,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
@@ -14449,7 +14449,7 @@
       </c>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O203" t="n">
         <v>2</v>
@@ -14490,12 +14490,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
@@ -14523,7 +14523,7 @@
         <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O204" t="n">
         <v>1.2</v>
@@ -14568,12 +14568,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O205" t="n">
         <v>2</v>
@@ -14628,12 +14628,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
@@ -14661,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O206" t="n">
         <v>1.2</v>
@@ -14706,12 +14706,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O207" t="n">
         <v>2</v>
@@ -14766,12 +14766,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
@@ -14799,7 +14799,7 @@
         <v>1</v>
       </c>
       <c r="N208" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O208" t="n">
         <v>1.2</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O209" t="n">
         <v>2</v>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
@@ -14937,7 +14937,7 @@
         <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O210" t="n">
         <v>1.2</v>
@@ -14982,12 +14982,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O211" t="n">
         <v>2</v>
@@ -15042,12 +15042,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
         <v>1</v>
       </c>
       <c r="N212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O212" t="n">
         <v>1.2</v>
@@ -15120,12 +15120,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O213" t="n">
         <v>2</v>
@@ -15180,12 +15180,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
@@ -15213,7 +15213,7 @@
         <v>1</v>
       </c>
       <c r="N214" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O214" t="n">
         <v>1.2</v>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O215" t="n">
         <v>2</v>
@@ -15318,12 +15318,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
@@ -15351,7 +15351,7 @@
         <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O216" t="n">
         <v>1.2</v>
@@ -15396,12 +15396,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O217" t="n">
         <v>2</v>
@@ -15456,12 +15456,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
@@ -15489,7 +15489,7 @@
         <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O218" t="n">
         <v>1.2</v>
@@ -15534,12 +15534,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O219" t="n">
         <v>2</v>
@@ -15594,12 +15594,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
@@ -15627,7 +15627,7 @@
         <v>1</v>
       </c>
       <c r="N220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O220" t="n">
         <v>1.2</v>
@@ -15672,12 +15672,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O221" t="n">
         <v>2</v>
@@ -15732,12 +15732,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
@@ -15765,7 +15765,7 @@
         <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O222" t="n">
         <v>1.2</v>
@@ -15810,12 +15810,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O223" t="n">
         <v>2</v>
@@ -15870,12 +15870,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
@@ -15903,7 +15903,7 @@
         <v>1</v>
       </c>
       <c r="N224" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O224" t="n">
         <v>1.2</v>
@@ -15948,12 +15948,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
@@ -15967,7 +15967,7 @@
       </c>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O225" t="n">
         <v>2</v>
@@ -16008,12 +16008,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
@@ -16041,7 +16041,7 @@
         <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O226" t="n">
         <v>1.2</v>
@@ -16086,12 +16086,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O227" t="n">
         <v>2</v>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
         <v>1</v>
       </c>
       <c r="N228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O228" t="n">
         <v>1.2</v>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O229" t="n">
         <v>2</v>
@@ -16284,12 +16284,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
@@ -16317,7 +16317,7 @@
         <v>1</v>
       </c>
       <c r="N230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O230" t="n">
         <v>1.2</v>
@@ -16362,12 +16362,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O231" t="n">
         <v>2</v>
@@ -16422,12 +16422,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
@@ -16455,7 +16455,7 @@
         <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O232" t="n">
         <v>1.2</v>
@@ -16500,12 +16500,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O233" t="n">
         <v>2</v>
@@ -16560,12 +16560,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
@@ -16593,7 +16593,7 @@
         <v>1</v>
       </c>
       <c r="N234" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O234" t="n">
         <v>1.2</v>
@@ -16638,12 +16638,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O235" t="n">
         <v>2</v>
@@ -16698,12 +16698,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
@@ -16731,7 +16731,7 @@
         <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O236" t="n">
         <v>1.2</v>
@@ -16776,12 +16776,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O237" t="n">
         <v>2</v>
@@ -16836,12 +16836,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
@@ -16869,7 +16869,7 @@
         <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O238" t="n">
         <v>1.2</v>
@@ -16914,12 +16914,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="M239" t="inlineStr"/>
       <c r="N239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O239" t="n">
         <v>2</v>
@@ -16974,12 +16974,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
@@ -17007,7 +17007,7 @@
         <v>1</v>
       </c>
       <c r="N240" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O240" t="n">
         <v>1.2</v>
@@ -17052,12 +17052,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O241" t="n">
         <v>2</v>
@@ -17112,12 +17112,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
@@ -17145,7 +17145,7 @@
         <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O242" t="n">
         <v>1.2</v>
@@ -17190,12 +17190,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="M243" t="inlineStr"/>
       <c r="N243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O243" t="n">
         <v>2</v>
@@ -17250,12 +17250,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
@@ -17283,7 +17283,7 @@
         <v>1</v>
       </c>
       <c r="N244" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O244" t="n">
         <v>1.2</v>
@@ -17328,12 +17328,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="M245" t="inlineStr"/>
       <c r="N245" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O245" t="n">
         <v>2</v>
@@ -17388,12 +17388,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
@@ -17421,7 +17421,7 @@
         <v>1</v>
       </c>
       <c r="N246" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O246" t="n">
         <v>1.2</v>
@@ -17466,12 +17466,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="M247" t="inlineStr"/>
       <c r="N247" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O247" t="n">
         <v>2</v>
@@ -17526,12 +17526,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
@@ -17559,7 +17559,7 @@
         <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O248" t="n">
         <v>1.2</v>
@@ -17604,12 +17604,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="M249" t="inlineStr"/>
       <c r="N249" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O249" t="n">
         <v>2</v>
@@ -17664,12 +17664,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
@@ -17697,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="N250" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O250" t="n">
         <v>1.2</v>
@@ -17742,12 +17742,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="M251" t="inlineStr"/>
       <c r="N251" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O251" t="n">
         <v>2</v>
@@ -17802,12 +17802,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
@@ -17835,7 +17835,7 @@
         <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O252" t="n">
         <v>1.2</v>
@@ -17880,12 +17880,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
@@ -17899,7 +17899,7 @@
       </c>
       <c r="M253" t="inlineStr"/>
       <c r="N253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O253" t="n">
         <v>2</v>
@@ -17940,12 +17940,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
@@ -17973,7 +17973,7 @@
         <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O254" t="n">
         <v>1.2</v>
@@ -18018,12 +18018,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H255" t="inlineStr"/>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O255" t="n">
         <v>2</v>
@@ -18078,12 +18078,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H256" t="inlineStr"/>
@@ -18111,7 +18111,7 @@
         <v>1</v>
       </c>
       <c r="N256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O256" t="n">
         <v>1.2</v>
@@ -18156,12 +18156,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
@@ -18175,7 +18175,7 @@
       </c>
       <c r="M257" t="inlineStr"/>
       <c r="N257" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O257" t="n">
         <v>2</v>
@@ -18216,12 +18216,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
@@ -18249,7 +18249,7 @@
         <v>1</v>
       </c>
       <c r="N258" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O258" t="n">
         <v>1.2</v>
@@ -18294,12 +18294,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H259" t="inlineStr"/>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="M259" t="inlineStr"/>
       <c r="N259" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O259" t="n">
         <v>2</v>
@@ -18354,12 +18354,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H260" t="inlineStr"/>
@@ -18387,7 +18387,7 @@
         <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O260" t="n">
         <v>1.2</v>
@@ -18432,12 +18432,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="H261" t="inlineStr"/>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="M261" t="inlineStr"/>
       <c r="N261" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O261" t="n">
         <v>2</v>
@@ -18492,12 +18492,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H262" t="inlineStr"/>
@@ -18525,7 +18525,7 @@
         <v>1</v>
       </c>
       <c r="N262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O262" t="n">
         <v>1.2</v>
@@ -18570,12 +18570,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H263" t="inlineStr"/>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="M263" t="inlineStr"/>
       <c r="N263" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O263" t="n">
         <v>2</v>
@@ -18630,12 +18630,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H264" t="inlineStr"/>
@@ -18663,7 +18663,7 @@
         <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O264" t="n">
         <v>1.2</v>
@@ -18708,12 +18708,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H265" t="inlineStr"/>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="M265" t="inlineStr"/>
       <c r="N265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O265" t="n">
         <v>2</v>
@@ -18768,12 +18768,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H266" t="inlineStr"/>
@@ -18801,7 +18801,7 @@
         <v>0</v>
       </c>
       <c r="N266" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O266" t="n">
         <v>1.2</v>
@@ -18846,12 +18846,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/dog/dog_22.jpg</t>
         </is>
       </c>
       <c r="H267" t="inlineStr"/>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="M267" t="inlineStr"/>
       <c r="N267" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O267" t="n">
         <v>2</v>
@@ -18906,12 +18906,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H268" t="inlineStr"/>
@@ -18939,7 +18939,7 @@
         <v>1</v>
       </c>
       <c r="N268" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O268" t="n">
         <v>1.2</v>
@@ -18984,12 +18984,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H269" t="inlineStr"/>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="M269" t="inlineStr"/>
       <c r="N269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O269" t="n">
         <v>2</v>
@@ -19044,12 +19044,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H270" t="inlineStr"/>
@@ -19077,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="N270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O270" t="n">
         <v>1.2</v>
@@ -19122,12 +19122,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H271" t="inlineStr"/>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="M271" t="inlineStr"/>
       <c r="N271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O271" t="n">
         <v>2</v>
@@ -19182,12 +19182,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H272" t="inlineStr"/>
@@ -19215,7 +19215,7 @@
         <v>0</v>
       </c>
       <c r="N272" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O272" t="n">
         <v>1.2</v>
@@ -19260,12 +19260,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="H273" t="inlineStr"/>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="M273" t="inlineStr"/>
       <c r="N273" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O273" t="n">
         <v>2</v>
@@ -19320,12 +19320,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="H274" t="inlineStr"/>
@@ -19353,7 +19353,7 @@
         <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O274" t="n">
         <v>1.2</v>
@@ -19398,12 +19398,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_29.jpg</t>
+          <t>stimuli/hammer/hammer_47.jpg</t>
         </is>
       </c>
       <c r="H275" t="inlineStr"/>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="M275" t="inlineStr"/>
       <c r="N275" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O275" t="n">
         <v>2</v>
@@ -19458,12 +19458,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H276" t="inlineStr"/>
@@ -19491,7 +19491,7 @@
         <v>1</v>
       </c>
       <c r="N276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O276" t="n">
         <v>1.2</v>
@@ -19536,12 +19536,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_20.jpg</t>
+          <t>stimuli/chair/chair_31.jpg</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_36.jpg</t>
+          <t>stimuli/house/house_46.jpg</t>
         </is>
       </c>
       <c r="H277" t="inlineStr"/>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="M277" t="inlineStr"/>
       <c r="N277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O277" t="n">
         <v>2</v>
@@ -19596,12 +19596,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H278" t="inlineStr"/>
@@ -19629,7 +19629,7 @@
         <v>1</v>
       </c>
       <c r="N278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O278" t="n">
         <v>1.2</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_47.jpg</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_43.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H279" t="inlineStr"/>
@@ -19693,7 +19693,7 @@
       </c>
       <c r="M279" t="inlineStr"/>
       <c r="N279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O279" t="n">
         <v>2</v>
@@ -19734,12 +19734,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H280" t="inlineStr"/>
@@ -19767,7 +19767,7 @@
         <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O280" t="n">
         <v>1.2</v>
@@ -19812,12 +19812,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_21.jpg</t>
+          <t>stimuli/flower/flower_16.jpg</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_21.jpg</t>
+          <t>stimuli/hand/hand_40.jpg</t>
         </is>
       </c>
       <c r="H281" t="inlineStr"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="M281" t="inlineStr"/>
       <c r="N281" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O281" t="n">
         <v>2</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="H282" t="inlineStr"/>
@@ -19905,7 +19905,7 @@
         <v>1</v>
       </c>
       <c r="N282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O282" t="n">
         <v>1.2</v>
@@ -19950,12 +19950,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="H283" t="inlineStr"/>
@@ -19969,7 +19969,7 @@
       </c>
       <c r="M283" t="inlineStr"/>
       <c r="N283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O283" t="n">
         <v>2</v>
@@ -20010,12 +20010,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H284" t="inlineStr"/>
@@ -20043,7 +20043,7 @@
         <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O284" t="n">
         <v>1.2</v>
@@ -20088,12 +20088,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H285" t="inlineStr"/>
@@ -20107,7 +20107,7 @@
       </c>
       <c r="M285" t="inlineStr"/>
       <c r="N285" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O285" t="n">
         <v>2</v>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H286" t="inlineStr"/>
@@ -20181,7 +20181,7 @@
         <v>1</v>
       </c>
       <c r="N286" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O286" t="n">
         <v>1.2</v>
@@ -20226,12 +20226,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="M287" t="inlineStr"/>
       <c r="N287" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O287" t="n">
         <v>2</v>
@@ -20286,12 +20286,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H288" t="inlineStr"/>
@@ -20319,7 +20319,7 @@
         <v>0</v>
       </c>
       <c r="N288" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O288" t="n">
         <v>1.2</v>
@@ -20364,12 +20364,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H289" t="inlineStr"/>
@@ -20383,7 +20383,7 @@
       </c>
       <c r="M289" t="inlineStr"/>
       <c r="N289" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O289" t="n">
         <v>2</v>
@@ -20424,12 +20424,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="H290" t="inlineStr"/>
@@ -20457,7 +20457,7 @@
         <v>0</v>
       </c>
       <c r="N290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O290" t="n">
         <v>1.2</v>
@@ -20502,12 +20502,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="H291" t="inlineStr"/>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="M291" t="inlineStr"/>
       <c r="N291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O291" t="n">
         <v>2</v>
@@ -20562,12 +20562,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H292" t="inlineStr"/>
@@ -20595,7 +20595,7 @@
         <v>1</v>
       </c>
       <c r="N292" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O292" t="n">
         <v>1.2</v>
@@ -20640,12 +20640,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H293" t="inlineStr"/>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="M293" t="inlineStr"/>
       <c r="N293" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O293" t="n">
         <v>2</v>
@@ -20700,12 +20700,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H294" t="inlineStr"/>
@@ -20733,7 +20733,7 @@
         <v>0</v>
       </c>
       <c r="N294" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O294" t="n">
         <v>1.2</v>
@@ -20778,12 +20778,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H295" t="inlineStr"/>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="M295" t="inlineStr"/>
       <c r="N295" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O295" t="n">
         <v>2</v>
@@ -20838,12 +20838,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H296" t="inlineStr"/>
@@ -20871,7 +20871,7 @@
         <v>1</v>
       </c>
       <c r="N296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O296" t="n">
         <v>1.2</v>
@@ -20916,12 +20916,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
@@ -20935,7 +20935,7 @@
       </c>
       <c r="M297" t="inlineStr"/>
       <c r="N297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O297" t="n">
         <v>2</v>
@@ -20976,12 +20976,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="H298" t="inlineStr"/>
@@ -21009,7 +21009,7 @@
         <v>1</v>
       </c>
       <c r="N298" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O298" t="n">
         <v>1.2</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_44.jpg</t>
         </is>
       </c>
       <c r="H299" t="inlineStr"/>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="M299" t="inlineStr"/>
       <c r="N299" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O299" t="n">
         <v>2</v>
@@ -21114,12 +21114,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H300" t="inlineStr"/>
@@ -21147,7 +21147,7 @@
         <v>0</v>
       </c>
       <c r="N300" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O300" t="n">
         <v>1.2</v>
@@ -21192,12 +21192,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H301" t="inlineStr"/>
@@ -21211,7 +21211,7 @@
       </c>
       <c r="M301" t="inlineStr"/>
       <c r="N301" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O301" t="n">
         <v>2</v>
@@ -21252,12 +21252,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H302" t="inlineStr"/>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="N302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O302" t="n">
         <v>1.2</v>
@@ -21330,12 +21330,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H303" t="inlineStr"/>
@@ -21349,7 +21349,7 @@
       </c>
       <c r="M303" t="inlineStr"/>
       <c r="N303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O303" t="n">
         <v>2</v>
@@ -21390,12 +21390,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H304" t="inlineStr"/>
@@ -21423,7 +21423,7 @@
         <v>1</v>
       </c>
       <c r="N304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O304" t="n">
         <v>1.2</v>
@@ -21468,12 +21468,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="M305" t="inlineStr"/>
       <c r="N305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O305" t="n">
         <v>2</v>
@@ -21528,12 +21528,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H306" t="inlineStr"/>
@@ -21561,7 +21561,7 @@
         <v>1</v>
       </c>
       <c r="N306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O306" t="n">
         <v>1.2</v>
@@ -21606,12 +21606,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H307" t="inlineStr"/>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="M307" t="inlineStr"/>
       <c r="N307" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O307" t="n">
         <v>2</v>
@@ -21666,12 +21666,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H308" t="inlineStr"/>
@@ -21699,7 +21699,7 @@
         <v>0</v>
       </c>
       <c r="N308" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O308" t="n">
         <v>1.2</v>
@@ -21744,12 +21744,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H309" t="inlineStr"/>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="M309" t="inlineStr"/>
       <c r="N309" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O309" t="n">
         <v>2</v>
@@ -21804,12 +21804,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H310" t="inlineStr"/>
@@ -21837,7 +21837,7 @@
         <v>0</v>
       </c>
       <c r="N310" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O310" t="n">
         <v>1.2</v>
@@ -21882,12 +21882,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_01.jpg</t>
+          <t>stimuli/dog/dog_32.jpg</t>
         </is>
       </c>
       <c r="H311" t="inlineStr"/>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="M311" t="inlineStr"/>
       <c r="N311" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O311" t="n">
         <v>2</v>
@@ -21942,12 +21942,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H312" t="inlineStr"/>
@@ -21975,7 +21975,7 @@
         <v>1</v>
       </c>
       <c r="N312" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O312" t="n">
         <v>1.2</v>
@@ -22020,12 +22020,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="H313" t="inlineStr"/>
@@ -22039,7 +22039,7 @@
       </c>
       <c r="M313" t="inlineStr"/>
       <c r="N313" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O313" t="n">
         <v>2</v>
@@ -22080,12 +22080,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H314" t="inlineStr"/>
@@ -22113,7 +22113,7 @@
         <v>0</v>
       </c>
       <c r="N314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O314" t="n">
         <v>1.2</v>
@@ -22158,12 +22158,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/chair/chair_08.jpg</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_23.jpg</t>
+          <t>stimuli/hand/hand_46.jpg</t>
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="M315" t="inlineStr"/>
       <c r="N315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O315" t="n">
         <v>2</v>
@@ -22218,12 +22218,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H316" t="inlineStr"/>
@@ -22251,7 +22251,7 @@
         <v>1</v>
       </c>
       <c r="N316" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O316" t="n">
         <v>1.2</v>
@@ -22296,12 +22296,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/house/house_24.jpg</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_37.jpg</t>
         </is>
       </c>
       <c r="H317" t="inlineStr"/>
@@ -22315,7 +22315,7 @@
       </c>
       <c r="M317" t="inlineStr"/>
       <c r="N317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O317" t="n">
         <v>2</v>
@@ -22356,12 +22356,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
@@ -22389,7 +22389,7 @@
         <v>0</v>
       </c>
       <c r="N318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O318" t="n">
         <v>1.2</v>
@@ -22434,12 +22434,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_42.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>stimuli/house/house_26.jpg</t>
+          <t>stimuli/jacket/jacket_36.jpg</t>
         </is>
       </c>
       <c r="H319" t="inlineStr"/>
@@ -22453,7 +22453,7 @@
       </c>
       <c r="M319" t="inlineStr"/>
       <c r="N319" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O319" t="n">
         <v>2</v>
@@ -22494,12 +22494,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H320" t="inlineStr"/>
@@ -22527,7 +22527,7 @@
         <v>1</v>
       </c>
       <c r="N320" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O320" t="n">
         <v>1.2</v>
@@ -22572,12 +22572,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_40.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="H321" t="inlineStr"/>
@@ -22591,7 +22591,7 @@
       </c>
       <c r="M321" t="inlineStr"/>
       <c r="N321" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O321" t="n">
         <v>2</v>

--- a/psychopy_exp_files/sequences/retrieval_block3_fixed-middle-10_56.xlsx
+++ b/psychopy_exp_files/sequences/retrieval_block3_fixed-middle-10_56.xlsx
@@ -567,12 +567,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -654,12 +654,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -723,12 +723,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -810,12 +810,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -879,12 +879,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -966,12 +966,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -2127,12 +2127,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -2682,12 +2682,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -3150,12 +3150,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -3219,12 +3219,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -3375,12 +3375,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -3999,12 +3999,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -4086,12 +4086,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -4311,12 +4311,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -4710,12 +4710,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -5022,12 +5022,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -5091,12 +5091,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5403,12 +5403,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -5490,12 +5490,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -5559,12 +5559,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -5646,12 +5646,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -5715,12 +5715,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -5802,12 +5802,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -5871,12 +5871,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -6027,12 +6027,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -6339,12 +6339,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -6495,12 +6495,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -6582,12 +6582,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -6738,12 +6738,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -6807,12 +6807,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -6963,12 +6963,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -7050,12 +7050,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -7119,12 +7119,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -7206,12 +7206,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -7275,12 +7275,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -7362,12 +7362,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -7518,12 +7518,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -7587,12 +7587,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -7743,12 +7743,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -8055,12 +8055,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -8142,12 +8142,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -8211,12 +8211,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -8298,12 +8298,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -8766,12 +8766,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -8835,12 +8835,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -8991,12 +8991,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -9078,12 +9078,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -9147,12 +9147,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -9303,12 +9303,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
@@ -9459,12 +9459,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -9546,12 +9546,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -9702,12 +9702,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -9771,12 +9771,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
@@ -10170,12 +10170,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -10239,12 +10239,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -10326,12 +10326,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -10395,12 +10395,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -10638,12 +10638,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -10707,12 +10707,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -10794,12 +10794,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -11019,12 +11019,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -11106,12 +11106,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -11331,12 +11331,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -11487,12 +11487,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -11574,12 +11574,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -11643,12 +11643,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -11799,12 +11799,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -11886,12 +11886,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -11955,12 +11955,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
@@ -12042,12 +12042,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -12203,7 +12203,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -12267,12 +12267,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -12354,12 +12354,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -12423,12 +12423,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
@@ -12510,12 +12510,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -12735,12 +12735,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
@@ -12822,12 +12822,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -13047,12 +13047,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
@@ -13134,12 +13134,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
@@ -13203,12 +13203,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -13290,12 +13290,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
@@ -13359,12 +13359,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
@@ -13515,12 +13515,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
@@ -13671,12 +13671,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
@@ -13758,12 +13758,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
@@ -13827,12 +13827,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -13914,12 +13914,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
@@ -13983,12 +13983,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
@@ -14070,12 +14070,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
@@ -14139,12 +14139,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -14226,12 +14226,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
@@ -14382,12 +14382,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
@@ -14451,12 +14451,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
@@ -14538,12 +14538,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
@@ -14607,12 +14607,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
@@ -14694,12 +14694,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
@@ -14763,12 +14763,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
@@ -14850,12 +14850,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
@@ -14919,12 +14919,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
@@ -15006,12 +15006,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
@@ -15075,12 +15075,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
@@ -15318,12 +15318,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
@@ -15387,12 +15387,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
@@ -15474,12 +15474,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
@@ -15543,12 +15543,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
@@ -15630,12 +15630,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
@@ -15699,12 +15699,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
@@ -15786,12 +15786,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
@@ -15855,12 +15855,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
@@ -15942,12 +15942,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
@@ -16011,12 +16011,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
@@ -16098,12 +16098,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
@@ -16167,12 +16167,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
@@ -16254,12 +16254,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
@@ -16323,12 +16323,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
@@ -16410,12 +16410,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
@@ -16479,12 +16479,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
@@ -16566,12 +16566,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
@@ -16791,12 +16791,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
@@ -16878,12 +16878,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
@@ -16947,12 +16947,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
@@ -17034,12 +17034,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
@@ -17103,12 +17103,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
@@ -17190,12 +17190,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
@@ -17351,7 +17351,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
@@ -17415,12 +17415,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
@@ -17502,12 +17502,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
@@ -17571,12 +17571,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
@@ -17658,12 +17658,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
@@ -17727,7 +17727,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
@@ -17970,12 +17970,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
@@ -18039,12 +18039,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
@@ -18195,12 +18195,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
@@ -18282,12 +18282,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
@@ -18351,12 +18351,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
@@ -18438,12 +18438,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
@@ -18507,12 +18507,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
@@ -18594,12 +18594,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
@@ -18663,12 +18663,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
@@ -18750,12 +18750,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
@@ -18819,12 +18819,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
@@ -18906,12 +18906,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
@@ -18975,12 +18975,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
@@ -19062,12 +19062,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
@@ -19136,7 +19136,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
@@ -19287,12 +19287,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
@@ -19374,12 +19374,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
@@ -19443,12 +19443,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
@@ -19530,12 +19530,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
@@ -19599,12 +19599,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
@@ -19686,12 +19686,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
@@ -19755,12 +19755,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
@@ -19842,12 +19842,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
@@ -19911,12 +19911,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
@@ -19998,12 +19998,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
@@ -20067,12 +20067,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
@@ -20154,12 +20154,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
@@ -20223,12 +20223,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
@@ -20310,12 +20310,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="H255" t="inlineStr"/>
@@ -20379,12 +20379,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H256" t="inlineStr"/>
@@ -20466,12 +20466,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
@@ -20535,12 +20535,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
@@ -20622,12 +20622,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H259" t="inlineStr"/>
@@ -20691,12 +20691,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="H260" t="inlineStr"/>
@@ -20778,12 +20778,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="H261" t="inlineStr"/>
@@ -20847,12 +20847,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H262" t="inlineStr"/>
@@ -20934,12 +20934,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="H263" t="inlineStr"/>
@@ -21003,12 +21003,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H264" t="inlineStr"/>
@@ -21090,12 +21090,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H265" t="inlineStr"/>
@@ -21159,12 +21159,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H266" t="inlineStr"/>
@@ -21246,12 +21246,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/ball/ball_38.jpg</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="H267" t="inlineStr"/>
@@ -21315,12 +21315,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H268" t="inlineStr"/>
@@ -21402,12 +21402,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H269" t="inlineStr"/>
@@ -21471,12 +21471,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H270" t="inlineStr"/>
@@ -21558,12 +21558,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H271" t="inlineStr"/>
@@ -21627,12 +21627,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="H272" t="inlineStr"/>
@@ -21714,12 +21714,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_46.jpg</t>
+          <t>stimuli/hand/hand_41.jpg</t>
         </is>
       </c>
       <c r="H273" t="inlineStr"/>
@@ -21783,12 +21783,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H274" t="inlineStr"/>
@@ -21870,12 +21870,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_10.jpg</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>stimuli/house/house_24.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H275" t="inlineStr"/>
@@ -21939,12 +21939,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H276" t="inlineStr"/>
@@ -22026,12 +22026,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_32.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H277" t="inlineStr"/>
@@ -22095,12 +22095,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="H278" t="inlineStr"/>
@@ -22182,12 +22182,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/hammer/hammer_10.jpg</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_08.jpg</t>
+          <t>stimuli/chair/chair_09.jpg</t>
         </is>
       </c>
       <c r="H279" t="inlineStr"/>
@@ -22251,12 +22251,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H280" t="inlineStr"/>
@@ -22338,12 +22338,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_36.jpg</t>
+          <t>stimuli/jacket/jacket_25.jpg</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H281" t="inlineStr"/>
@@ -22407,12 +22407,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H282" t="inlineStr"/>
@@ -22494,12 +22494,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H283" t="inlineStr"/>
@@ -22563,12 +22563,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H284" t="inlineStr"/>
@@ -22650,12 +22650,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H285" t="inlineStr"/>
@@ -22719,12 +22719,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H286" t="inlineStr"/>
@@ -22806,12 +22806,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
@@ -22880,7 +22880,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H288" t="inlineStr"/>
@@ -22967,7 +22967,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H289" t="inlineStr"/>
@@ -23031,12 +23031,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H290" t="inlineStr"/>
@@ -23118,12 +23118,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H291" t="inlineStr"/>
@@ -23187,12 +23187,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H292" t="inlineStr"/>
@@ -23274,12 +23274,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H293" t="inlineStr"/>
@@ -23343,12 +23343,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H294" t="inlineStr"/>
@@ -23430,12 +23430,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="H295" t="inlineStr"/>
@@ -23504,7 +23504,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H296" t="inlineStr"/>
@@ -23591,7 +23591,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
@@ -23655,12 +23655,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H298" t="inlineStr"/>
@@ -23742,12 +23742,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>stimuli/house/house_46.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H299" t="inlineStr"/>
@@ -23811,12 +23811,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H300" t="inlineStr"/>
@@ -23898,12 +23898,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H301" t="inlineStr"/>
@@ -23967,12 +23967,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H302" t="inlineStr"/>
@@ -24054,12 +24054,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="H303" t="inlineStr"/>
@@ -24123,12 +24123,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H304" t="inlineStr"/>
@@ -24210,12 +24210,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
@@ -24279,12 +24279,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H306" t="inlineStr"/>
@@ -24366,12 +24366,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H307" t="inlineStr"/>
@@ -24435,12 +24435,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H308" t="inlineStr"/>
@@ -24522,12 +24522,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bread/bread_02.jpg</t>
         </is>
       </c>
       <c r="H309" t="inlineStr"/>
@@ -24591,12 +24591,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H310" t="inlineStr"/>
@@ -24678,12 +24678,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H311" t="inlineStr"/>
@@ -24752,7 +24752,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H312" t="inlineStr"/>
@@ -24839,7 +24839,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H313" t="inlineStr"/>
@@ -24903,12 +24903,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H314" t="inlineStr"/>
@@ -24990,12 +24990,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_31.jpg</t>
+          <t>stimuli/chair/chair_01.jpg</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_47.jpg</t>
+          <t>stimuli/hammer/hammer_31.jpg</t>
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
@@ -25059,12 +25059,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H316" t="inlineStr"/>
@@ -25146,12 +25146,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_47.jpg</t>
+          <t>stimuli/bicycle/bicycle_21.jpg</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_22.jpg</t>
+          <t>stimuli/dog/dog_18.jpg</t>
         </is>
       </c>
       <c r="H317" t="inlineStr"/>
@@ -25215,12 +25215,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
@@ -25302,12 +25302,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_47.jpg</t>
         </is>
       </c>
       <c r="H319" t="inlineStr"/>
@@ -25376,7 +25376,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H320" t="inlineStr"/>
@@ -25463,7 +25463,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H321" t="inlineStr"/>
